--- a/it_request_forms/018_social_media_account_linking_support_request--it_request_forms.xlsx
+++ b/it_request_forms/018_social_media_account_linking_support_request--it_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -876,8 +876,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,12 +905,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'snapchat'}</t>
+          <t>snapchat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Snapchat'}</t>
+          <t>Snapchat</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'tiktok'}</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'TikTok'}</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'deleted'}</t>
+          <t>deleted</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Deleted'}</t>
+          <t>Deleted</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'suspended'}</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Suspended'}</t>
+          <t>Suspended</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'human_agent'}</t>
+          <t>human_agent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Human Agent'}</t>
+          <t>Human Agent</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'automated_bot'}</t>
+          <t>automated_bot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Automated Bot'}</t>
+          <t>Automated Bot</t>
         </is>
       </c>
     </row>
